--- a/output/peer_comparison.xlsx
+++ b/output/peer_comparison.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Automobiles" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Consumer Finance" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FMCG" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="IT Services" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Life Insurance" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Oil &amp; Gas" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pharmaceuticals" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power &amp; Utilities" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Private Banks" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Public Sector Banks" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steel" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Automobiles" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Consumer Finance" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="FMCG" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="IT Services" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Life Insurance" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Oil &amp; Gas" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Pharmaceuticals" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Power &amp; Utilities" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Private Banks" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Public Sector Banks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Steel" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/output/peer_comparison.xlsx
+++ b/output/peer_comparison.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,14 +37,25 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E78"/>
+        <bgColor rgb="001F4E78"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -66,8 +77,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-        <bgColor rgb="00FFE699"/>
+        <fgColor rgb="00FFD966"/>
+        <bgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
   </fills>
@@ -83,13 +94,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -458,137 +470,137 @@
   <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -606,16 +618,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>24.88137125149295</v>
+        <v>26.61418410330778</v>
       </c>
       <c r="D2" t="n">
-        <v>28.88968639575972</v>
+        <v>27.20735894279976</v>
       </c>
       <c r="E2" t="n">
         <v>17.17851571205706</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1693082410665289</v>
+        <v>0.06601754022512257</v>
       </c>
       <c r="G2" t="n">
         <v>6486</v>
@@ -633,37 +645,37 @@
         <v>174.4166666666667</v>
       </c>
       <c r="L2" t="n">
-        <v>0.978796736617076</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>0.8333</v>
+        <v>1.140453436356242</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.8571</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>0.8333</v>
+        <v>0.8571</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>0.8571</v>
       </c>
       <c r="R2" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.5714</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>0.5714</v>
       </c>
     </row>
     <row r="3">
@@ -678,16 +690,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>21.08119500500553</v>
+        <v>22.17234691050152</v>
       </c>
       <c r="D3" t="n">
-        <v>30.18108651911469</v>
+        <v>20.20688908145581</v>
       </c>
       <c r="E3" t="n">
         <v>24.19569424286405</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02128668528373465</v>
+        <v>0.02321972845663619</v>
       </c>
       <c r="G3" t="n">
         <v>890</v>
@@ -705,37 +717,37 @@
         <v>114.7058823529412</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6782608695652174</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N3" s="2" t="n">
+        <v>0.7153796236210254</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="R3" s="3" t="n">
         <v>0.6667</v>
       </c>
-      <c r="O3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="R3" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="U3" s="2" t="n">
+      <c r="S3" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="T3" s="3" t="n">
         <v>0.6667</v>
       </c>
+      <c r="U3" s="3" t="n">
+        <v>0.7143</v>
+      </c>
       <c r="V3" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="4">
@@ -746,21 +758,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hero MotoCorp Ltd
-</t>
+          <t>Hero MotoCorp Ltd</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>19.68334122350218</v>
+        <v>21.14243742584327</v>
       </c>
       <c r="D4" t="n">
-        <v>166.1717434562988</v>
+        <v>173.7066375307293</v>
       </c>
       <c r="E4" t="n">
         <v>9.902352536452407</v>
       </c>
       <c r="F4" t="n">
-        <v>0.03092946189048446</v>
+        <v>0.03423922255494661</v>
       </c>
       <c r="G4" t="n">
         <v>3095</v>
@@ -778,36 +789,36 @@
         <v>47.26850507982584</v>
       </c>
       <c r="L4" t="n">
-        <v>1.291445951949694</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V4" s="1" t="n">
+        <v>1.444920276832486</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="R4" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="T4" s="4" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -819,21 +830,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mahindra &amp; Mahindra Ltd
-</t>
+          <t>Mahindra &amp; Mahindra Ltd</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>17.40376159541573</v>
+        <v>18.53754343556428</v>
       </c>
       <c r="D5" t="n">
-        <v>15.04702529010494</v>
+        <v>11.53531575124259</v>
       </c>
       <c r="E5" t="n">
         <v>8.822387437265419</v>
       </c>
       <c r="F5" t="n">
-        <v>1.657314686108196</v>
+        <v>1.641441305333132</v>
       </c>
       <c r="G5" t="n">
         <v>-11245</v>
@@ -851,109 +861,109 @@
         <v>3.764690170940171</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5448057035412096</v>
+        <v>0.5925222177725139</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P5" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1" t="n">
-        <v>0.8</v>
+        <v>0.2857</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="R5" s="2" t="n">
+        <v>0.8333</v>
       </c>
       <c r="S5" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="T5" s="1" t="n">
-        <v>0.8</v>
+        <v>0.2857</v>
+      </c>
+      <c r="T5" s="2" t="n">
+        <v>0.8333</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0</v>
+        <v>0.2857</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>0.1429</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>MARUTI</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Maruti Suzuki India Ltd</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>15.13363103920293</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>25.61937189194033</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="C6" s="5" t="n">
+        <v>15.75038535195478</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>15.59092764270305</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>9.50809964894472</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0.001772771133002715</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="F6" s="5" t="n">
+        <v>0.001389602503619973</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>4936</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>12.00718203930038</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>10.51021511264258</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="5" t="n">
         <v>11.1392224868865</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <v>117.9072164948454</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>1.165675124901394</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="O6" s="4" t="n">
+      <c r="L6" s="5" t="n">
+        <v>1.230295566502463</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="R6" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="P6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0.8333</v>
+      <c r="S6" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0.8571</v>
       </c>
     </row>
     <row r="7">
@@ -968,56 +978,64 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>31.47275929627357</v>
+        <v>37.45613415294755</v>
       </c>
       <c r="D7" t="n">
-        <v>31.41018539480086</v>
+        <v>16.79050889790821</v>
       </c>
       <c r="E7" t="n">
         <v>7.263066074788551</v>
       </c>
       <c r="F7" t="n">
-        <v>1.054293404049</v>
+        <v>1.263124425916767</v>
       </c>
       <c r="G7" t="n">
         <v>45133</v>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="n">
+        <v/>
+      </c>
       <c r="I7" t="n">
         <v>7.720159538623927</v>
       </c>
-      <c r="J7" t="inlineStr"/>
+      <c r="J7" t="n">
+        <v/>
+      </c>
       <c r="K7" t="n">
         <v>6.530242339274985</v>
       </c>
       <c r="L7" t="n">
-        <v>1.121006716906946</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.8333</v>
+        <v>1.185123443593192</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>0.5714</v>
       </c>
       <c r="O7" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.2857</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="T7" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0.7143</v>
       </c>
     </row>
     <row r="8">
@@ -1032,16 +1050,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>22.92525773195876</v>
+        <v>26.22346698113208</v>
       </c>
       <c r="D8" t="n">
-        <v>25.05027034273202</v>
+        <v>13.79993900579445</v>
       </c>
       <c r="E8" t="n">
         <v>4.544641716694342</v>
       </c>
       <c r="F8" t="n">
-        <v>1.88389175257732</v>
+        <v>3.833431603773585</v>
       </c>
       <c r="G8" t="n">
         <v>-2254</v>
@@ -1059,86 +1077,86 @@
         <v>2.907676348547718</v>
       </c>
       <c r="L8" t="n">
-        <v>0.8709340097005295</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.9314915286502951</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.7143</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="O8" s="3" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="P8" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.2857</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="V8" s="3" t="n">
+        <v>0.4286</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>21.08119500500553</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>28.88968639575972</v>
-      </c>
-      <c r="E9" s="5" t="n">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>22.17234691050152</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>16.79050889790821</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>9.50809964894472</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>0.1693082410665289</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="F9" s="6" t="n">
+        <v>0.06601754022512257</v>
+      </c>
+      <c r="G9" s="6" t="n">
         <v>3095</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <v>12.34151185233904</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="6" t="n">
         <v>8.127604751021389</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <v>11.82233705796841</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="6" t="n">
         <v>47.26850507982584</v>
       </c>
-      <c r="L9" s="5" t="n">
-        <v>0.978796736617076</v>
-      </c>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr"/>
+      <c r="L9" s="6" t="n">
+        <v>1.140453436356242</v>
+      </c>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
+      <c r="T9" s="6" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1154,137 +1172,137 @@
   <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -1305,7 +1323,7 @@
         <v>15.7618637908999</v>
       </c>
       <c r="D2" t="n">
-        <v>2.820637646379921</v>
+        <v>2.712278690337432</v>
       </c>
       <c r="E2" t="n">
         <v>15.93948250956673</v>
@@ -1332,34 +1350,34 @@
         <v>0.07153782236255685</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="Q2" s="2" t="n">
+      <c r="Q2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="R2" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="S2" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T2" s="3" t="n">
         <v>0.6667</v>
       </c>
-      <c r="T2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U2" s="1" t="n">
+      <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="3">
@@ -1377,7 +1395,7 @@
         <v>16.71605179468811</v>
       </c>
       <c r="D3" t="n">
-        <v>3.156070162861949</v>
+        <v>3.09484900948278</v>
       </c>
       <c r="E3" t="n">
         <v>13.93516047014541</v>
@@ -1403,35 +1421,35 @@
       <c r="L3" t="n">
         <v>0.0719985042520674</v>
       </c>
-      <c r="M3" s="2" t="n">
+      <c r="M3" s="3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="2" t="n">
+      <c r="P3" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="3" t="n">
         <v>0.3333</v>
       </c>
-      <c r="P3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
+      <c r="U3" s="3" t="n">
         <v>0.6667</v>
       </c>
-      <c r="R3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="2" t="n">
+      <c r="V3" s="3" t="n">
         <v>0.6667</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -1448,7 +1466,9 @@
       <c r="C4" t="n">
         <v>61.32056519118731</v>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="n">
+        <v/>
+      </c>
       <c r="E4" t="n">
         <v>8.395910695456838</v>
       </c>
@@ -1458,149 +1478,171 @@
       <c r="G4" t="n">
         <v>-29445</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v/>
+      </c>
       <c r="I4" t="n">
         <v>15.90207600910603</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v/>
+      </c>
       <c r="K4" t="n">
-        <v>0.2065835935448099</v>
+        <v/>
       </c>
       <c r="L4" t="n">
         <v>1.50702629506294</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v/>
+      </c>
       <c r="O4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P4" s="3" t="n">
         <v>0.6667</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" s="2" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R4" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>SBIN</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>State Bank of India</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>15.83441297482405</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>18156</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>83.40695423292949</v>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>11.63380022632805</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>90.36539387158786</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>0.3660986540179259</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" s="5" t="n">
         <v>0.3333</v>
       </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>SBIN</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>State Bank of India</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="n">
-        <v>15.83441297482405</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>18156</v>
-      </c>
-      <c r="H5" s="4" t="n">
+      <c r="V5" s="5" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="n">
+        <v>16.71605179468811</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>2.903563849910106</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>14.88478672248473</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>12.14371872728943</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2868.5</v>
+      </c>
+      <c r="H6" s="6" t="n">
         <v>83.40695423292949</v>
       </c>
-      <c r="I5" s="4" t="n">
-        <v>11.63380022632805</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>90.36539387158786</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>0.3660986540179259</v>
-      </c>
-      <c r="L5" s="4" t="inlineStr"/>
-      <c r="M5" s="4" t="inlineStr"/>
-      <c r="N5" s="4" t="inlineStr"/>
-      <c r="O5" s="4" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="V5" s="4" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>16.71605179468811</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>2.988353904620935</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>14.88478672248473</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>7.913987536148568</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>2868.5</v>
-      </c>
-      <c r="H6" s="5" t="n">
-        <v>83.40695423292949</v>
-      </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <v>16.68968683749848</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>55.18455739153598</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v>0.9883799141764558</v>
-      </c>
-      <c r="L6" s="5" t="n">
+      <c r="K6" s="6" t="n">
+        <v>1.610661174334986</v>
+      </c>
+      <c r="L6" s="6" t="n">
         <v>0.0719985042520674</v>
       </c>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr"/>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1616,137 +1658,137 @@
   <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -1764,16 +1806,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8.816941029381121</v>
+        <v>9.567011474761177</v>
       </c>
       <c r="D2" t="n">
-        <v>109.0646379197775</v>
+        <v>113.5795251750748</v>
       </c>
       <c r="E2" t="n">
         <v>4.702216130615571</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5292682503299299</v>
+        <v>0.5309290976579428</v>
       </c>
       <c r="G2" t="n">
         <v>9789</v>
@@ -1791,36 +1833,36 @@
         <v>126.4654377880184</v>
       </c>
       <c r="L2" t="n">
-        <v>0.856095201852028</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="Q2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R2" s="1" t="n">
+        <v>0.9360228499109322</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Q2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S2" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1836,56 +1878,64 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>12.5536004731628</v>
+        <v>13.4105063633902</v>
       </c>
       <c r="D3" t="n">
-        <v>16.03231847942173</v>
+        <v>12.14055405672172</v>
       </c>
       <c r="E3" t="n">
         <v>11.80243873376494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3647155742379755</v>
+        <v>0.3716941962270963</v>
       </c>
       <c r="G3" t="n">
         <v>-2336</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v/>
+      </c>
       <c r="I3" t="n">
         <v>1.402831094774171</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v/>
+      </c>
       <c r="K3" t="n">
         <v>8.004636785162287</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6083531671720772</v>
-      </c>
-      <c r="M3" s="1" t="n">
+        <v>0.6400172860847018</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
+        <v>0.75</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v/>
+      </c>
       <c r="S3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
+        <v>0.25</v>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
       <c r="U3" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="4">
@@ -1900,16 +1950,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>11.26327416965832</v>
+        <v>11.5528718021347</v>
       </c>
       <c r="D4" t="n">
-        <v>16.95422011845144</v>
+        <v>12.06437553198553</v>
       </c>
       <c r="E4" t="n">
         <v>5.127252779904689</v>
       </c>
       <c r="F4" t="n">
-        <v>1.195717118971707</v>
+        <v>1.132807168883338</v>
       </c>
       <c r="G4" t="n">
         <v>-2389</v>
@@ -1927,151 +1977,158 @@
         <v>3.659099321406539</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7505575379125781</v>
+        <v>0.7679137157851319</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="P4" s="3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="R4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.5</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>0.5</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TATASTEEL</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Tata Steel Ltd
-</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>-5.44665934529158</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>8.569740264536586</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Tata Steel Ltd</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.334926929972293</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>6.903867304610952</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>-2.142504941724738</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>1.102554716185785</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F5" s="5" t="n">
+        <v>0.9461835171402184</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>6048</v>
       </c>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="n">
+      <c r="H5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="5" t="n">
         <v>7.766224835881497</v>
       </c>
-      <c r="J5" s="4" t="inlineStr"/>
-      <c r="K5" s="4" t="n">
+      <c r="J5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K5" s="5" t="n">
         <v>2.16342567927544</v>
       </c>
-      <c r="L5" s="4" t="n">
-        <v>0.8160168921204525</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="R5" s="4" t="inlineStr"/>
-      <c r="S5" s="4" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="T5" s="4" t="inlineStr"/>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0.6667</v>
+      <c r="L5" s="5" t="n">
+        <v>0.8509498277091255</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>10.04010759951972</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>16.49326929893659</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="n">
+        <v>10.55994163844794</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>12.10246479435363</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>4.914734455260129</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>0.8159114832578576</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="F6" s="6" t="n">
+        <v>0.7385563073990806</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>1856</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>8.326964175429985</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <v>9.179329327433706</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>7.890141658631844</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K6" s="6" t="n">
         <v>5.831868053284413</v>
       </c>
-      <c r="L6" s="5" t="n">
-        <v>0.7832872150165153</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr"/>
+      <c r="L6" s="6" t="n">
+        <v>0.8094317717471287</v>
+      </c>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2087,212 +2144,212 @@
   <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>BAJFINANCE</t>
         </is>
       </c>
-      <c r="B2" s="4" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>Bajaj Finance Ltd</t>
         </is>
       </c>
-      <c r="C2" s="4" t="n">
-        <v>16.64804211835996</v>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>3.92559017665764</v>
-      </c>
-      <c r="E2" s="4" t="n">
+      <c r="C2" s="5" t="n">
+        <v>18.8419213518306</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>4.166013587646808</v>
+      </c>
+      <c r="E2" s="5" t="n">
         <v>26.28792839991269</v>
       </c>
-      <c r="F2" s="4" t="n">
-        <v>3.735101321382901</v>
-      </c>
-      <c r="G2" s="4" t="n">
+      <c r="F2" s="5" t="n">
+        <v>3.824788776468134</v>
+      </c>
+      <c r="G2" s="5" t="n">
         <v>-79931</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>29.32313482597901</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="5" t="n">
         <v>24.35264273954201</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="5" t="n">
         <v>27.5561392815338</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="K2" s="5" t="n">
         <v>2689.166666666667</v>
       </c>
-      <c r="L2" s="4" t="n">
-        <v>0.1306816020691491</v>
-      </c>
-      <c r="M2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V2" s="4" t="n">
-        <v>0.5</v>
+      <c r="L2" s="5" t="n">
+        <v>0.1463025160881669</v>
+      </c>
+      <c r="M2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="Q2" s="5" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="R2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V2" s="5" t="n">
+        <v>0.6667</v>
       </c>
     </row>
     <row r="3">
@@ -2307,16 +2364,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>15.97309794031105</v>
+        <v>17.45521359669269</v>
       </c>
       <c r="D3" t="n">
-        <v>3.015823455289539</v>
+        <v>3.366695225484851</v>
       </c>
       <c r="E3" t="n">
         <v>17.84689244899024</v>
       </c>
       <c r="F3" t="n">
-        <v>7.376722245574705</v>
+        <v>6.863420609401317</v>
       </c>
       <c r="G3" t="n">
         <v>-38538</v>
@@ -2334,37 +2391,37 @@
         <v>21.21176470588235</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1053230371815659</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.1223019286981607</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.6667</v>
       </c>
       <c r="N3" s="3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="P3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0.5</v>
+      <c r="Q3" s="3" t="n">
+        <v>0.6667</v>
       </c>
       <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.6667</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
     </row>
     <row r="4">
@@ -2375,21 +2432,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shriram Finance Ltd
-</t>
+          <t>Shriram Finance Ltd</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>14.12238509696137</v>
+        <v>15.11635033812082</v>
       </c>
       <c r="D4" t="n">
-        <v>4.053617819316557</v>
+        <v>4.064342198385718</v>
       </c>
       <c r="E4" t="n">
         <v>20.33362647026492</v>
       </c>
       <c r="F4" t="n">
-        <v>3.966636127653077</v>
+        <v>3.994034363699512</v>
       </c>
       <c r="G4" t="n">
         <v>-31359</v>
@@ -2407,86 +2463,86 @@
         <v>0.6766743648960739</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1322781520028209</v>
+        <v>0.1465685998082702</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.3333</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.6667</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>0</v>
+        <v>0.3333</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" s="1" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="V4" s="2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr"/>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="n">
-        <v>15.97309794031105</v>
-      </c>
-      <c r="D5" s="5" t="n">
-        <v>3.92559017665764</v>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr"/>
+      <c r="C5" s="6" t="n">
+        <v>17.45521359669269</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>4.064342198385718</v>
+      </c>
+      <c r="E5" s="6" t="n">
         <v>20.33362647026492</v>
       </c>
-      <c r="F5" s="5" t="n">
-        <v>3.966636127653077</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="F5" s="6" t="n">
+        <v>3.994034363699512</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>-38538</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>23.49387942502037</v>
       </c>
-      <c r="I5" s="5" t="n">
+      <c r="I5" s="6" t="n">
         <v>21.93916480497526</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <v>22.27523876455795</v>
       </c>
-      <c r="K5" s="5" t="n">
+      <c r="K5" s="6" t="n">
         <v>21.21176470588235</v>
       </c>
-      <c r="L5" s="5" t="n">
-        <v>0.1306816020691491</v>
-      </c>
-      <c r="M5" s="5" t="inlineStr"/>
-      <c r="N5" s="5" t="inlineStr"/>
-      <c r="O5" s="5" t="inlineStr"/>
-      <c r="P5" s="5" t="inlineStr"/>
-      <c r="Q5" s="5" t="inlineStr"/>
-      <c r="R5" s="5" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr"/>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr"/>
-      <c r="V5" s="5" t="inlineStr"/>
+      <c r="L5" s="6" t="n">
+        <v>0.1463025160881669</v>
+      </c>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="6" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="6" t="n"/>
+      <c r="R5" s="6" t="n"/>
+      <c r="S5" s="6" t="n"/>
+      <c r="T5" s="6" t="n"/>
+      <c r="U5" s="6" t="n"/>
+      <c r="V5" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2502,137 +2558,137 @@
   <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -2650,16 +2706,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>66.47975077881621</v>
+        <v>54.14869322506978</v>
       </c>
       <c r="D2" t="n">
-        <v>56.63983903420523</v>
+        <v>47.73559773559774</v>
       </c>
       <c r="E2" t="n">
         <v>12.72586319995229</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8579439252336448</v>
+        <v>0.5239786856127886</v>
       </c>
       <c r="G2" t="n">
         <v>3050</v>
@@ -2677,37 +2733,37 @@
         <v>20.59756097560976</v>
       </c>
       <c r="L2" t="n">
-        <v>1.771310869335587</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="N2" s="2" t="n">
+        <v>1.848434744268078</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="R2" s="3" t="n">
         <v>0.6667</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="n">
+      <c r="S2" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="T2" s="3" t="n">
         <v>0.6667</v>
       </c>
-      <c r="R2" s="2" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>0.6</v>
-      </c>
       <c r="U2" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="V2" s="1" t="n">
-        <v>0.8333</v>
+        <v>0.2857</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0.8571</v>
       </c>
     </row>
     <row r="3">
@@ -2722,16 +2778,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.4773209805057</v>
+        <v>18.35596999797284</v>
       </c>
       <c r="D3" t="n">
-        <v>23.79065543998679</v>
+        <v>17.81675718992075</v>
       </c>
       <c r="E3" t="n">
         <v>14.60012899064818</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1690793283149971</v>
+        <v>0.1383539428339753</v>
       </c>
       <c r="G3" t="n">
         <v>1042</v>
@@ -2749,37 +2805,37 @@
         <v>23.24193548387097</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7575887131252672</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0</v>
+        <v>0.8205874569992061</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.1667</v>
       </c>
       <c r="S3" s="3" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="T3" s="4" t="n">
         <v>0.1667</v>
       </c>
-      <c r="T3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0.5</v>
+      <c r="U3" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>0.7143</v>
       </c>
     </row>
     <row r="4">
@@ -2794,129 +2850,136 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-4.609695973705834</v>
+        <v>-4.45308779171297</v>
       </c>
       <c r="D4" t="n">
-        <v>4.675584448056007</v>
+        <v>17.16814159292036</v>
       </c>
       <c r="E4" t="n">
         <v>-3.979852440408627</v>
       </c>
       <c r="F4" t="n">
-        <v>0.314543960558751</v>
+        <v>0.2557548817272583</v>
       </c>
       <c r="G4" t="n">
         <v>-1365</v>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="n">
+        <v/>
+      </c>
       <c r="I4" t="n">
         <v>6.447080048592069</v>
       </c>
-      <c r="J4" t="inlineStr"/>
+      <c r="J4" t="n">
+        <v/>
+      </c>
       <c r="K4" t="n">
         <v>2.412903225806452</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7425200168563001</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
+        <v>0.7664201826881253</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0.1429</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" s="3" t="n">
-        <v>0</v>
+        <v>0.2857</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="R4" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="T4" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="4" t="n">
+        <v>0.1429</v>
       </c>
       <c r="V4" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>HINDUNILVR</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hindustan Unilever Ltd
-</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="n">
-        <v>20.24972427918702</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>90.14629866290271</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Hindustan Unilever Ltd</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>20.07497364207896</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>87.32306174338734</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>16.61173581491534</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0.03251536158815188</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F5" s="5" t="n">
+        <v>0.02897418876176344</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>10145</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>11.15295043680342</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>9.504485244074123</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>9.460878422315755</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>57.8470012239902</v>
       </c>
-      <c r="L5" s="4" t="n">
-        <v>0.7663715718442394</v>
-      </c>
-      <c r="M5" s="4" t="n">
+      <c r="L5" s="5" t="n">
+        <v>0.7885945801322478</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="R5" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="N5" s="4" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0.6667</v>
+      <c r="S5" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0.5714</v>
       </c>
     </row>
     <row r="6">
@@ -2927,21 +2990,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">ITC Ltd
-</t>
+          <t>ITC Ltd</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>27.57021762814551</v>
+        <v>27.85107439569436</v>
       </c>
       <c r="D6" t="n">
-        <v>38.42397776895594</v>
+        <v>32.63868466782516</v>
       </c>
       <c r="E6" t="n">
         <v>29.28202523071713</v>
       </c>
       <c r="F6" t="n">
-        <v>0.004039008317168443</v>
+        <v>0.004066731984914169</v>
       </c>
       <c r="G6" t="n">
         <v>18742</v>
@@ -2959,37 +3021,37 @@
         <v>362.9625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7533246165130593</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="N6" s="2" t="n">
+        <v>0.7723477995509732</v>
+      </c>
+      <c r="M6" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="Q6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="S6" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="T6" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="O6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="S6" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="U6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>0.3333</v>
+      <c r="U6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0.4286</v>
       </c>
     </row>
     <row r="7">
@@ -3004,16 +3066,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>98.57142857142858</v>
+        <v>117.7544910179641</v>
       </c>
       <c r="D7" t="n">
-        <v>136.9724770642202</v>
+        <v>143.1478968792402</v>
       </c>
       <c r="E7" t="n">
         <v>16.12281708616873</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09273182957393483</v>
+        <v>0.1032934131736527</v>
       </c>
       <c r="G7" t="n">
         <v>2938</v>
@@ -3031,36 +3093,36 @@
         <v>41.18620689655172</v>
       </c>
       <c r="L7" t="n">
-        <v>2.196074900972272</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="Q7" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R7" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="S7" s="1" t="n">
+        <v>2.318160220469448</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="Q7" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="R7" s="2" t="n">
         <v>0.8333</v>
       </c>
-      <c r="T7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="V7" s="1" t="n">
+      <c r="S7" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="V7" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3076,16 +3138,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.350616767719004</v>
+        <v>7.566793298872766</v>
       </c>
       <c r="D8" t="n">
-        <v>9.974192964187079</v>
+        <v>9.762465444865363</v>
       </c>
       <c r="E8" t="n">
         <v>7.990266999868473</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1544532720050178</v>
+        <v>0.21654107242947</v>
       </c>
       <c r="G8" t="n">
         <v>26</v>
@@ -3103,86 +3165,86 @@
         <v>25.32183908045977</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4909912818856959</v>
+        <v>0.5454284586965099</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="N8" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.2857</v>
+      </c>
+      <c r="N8" s="4" t="n">
+        <v>0.1429</v>
       </c>
       <c r="O8" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="P8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.2857</v>
+      </c>
+      <c r="P8" s="3" t="n">
+        <v>0.2857</v>
       </c>
       <c r="Q8" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T8" s="1" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>0</v>
+        <v>0.2857</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>0.8333</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>0.1429</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>20.24972427918702</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>38.42397776895594</v>
-      </c>
-      <c r="E9" s="5" t="n">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>20.07497364207896</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>32.63868466782516</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>14.60012899064818</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>0.1544532720050178</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="F9" s="6" t="n">
+        <v>0.1383539428339753</v>
+      </c>
+      <c r="G9" s="6" t="n">
         <v>2938</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <v>12.10823313212881</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="6" t="n">
         <v>8.690023727476138</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <v>11.49979601455158</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="6" t="n">
         <v>25.32183908045977</v>
       </c>
-      <c r="L9" s="5" t="n">
-        <v>0.7575887131252672</v>
-      </c>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr"/>
+      <c r="L9" s="6" t="n">
+        <v>0.7885945801322478</v>
+      </c>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
+      <c r="T9" s="6" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3198,137 +3260,137 @@
   <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -3346,16 +3408,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>22.80943738656987</v>
+        <v>23.01393141233172</v>
       </c>
       <c r="D2" t="n">
-        <v>34.41057509442049</v>
+        <v>27.05313357020305</v>
       </c>
       <c r="E2" t="n">
         <v>14.29312274253273</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08407985480943739</v>
+        <v>0.08435023365512796</v>
       </c>
       <c r="G2" t="n">
         <v>15840</v>
@@ -3373,37 +3435,37 @@
         <v>46.46112115732369</v>
       </c>
       <c r="L2" t="n">
-        <v>1.101741126469733</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P2" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>0.25</v>
+        <v>1.110165040502596</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V2" s="4" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -3418,16 +3480,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>29.01517747587411</v>
+        <v>29.78800671841663</v>
       </c>
       <c r="D3" t="n">
-        <v>41.43975339236604</v>
+        <v>32.90697071780254</v>
       </c>
       <c r="E3" t="n">
         <v>17.08075746730006</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09732155687960824</v>
+        <v>0.09486358890553362</v>
       </c>
       <c r="G3" t="n">
         <v>20117</v>
@@ -3445,37 +3507,37 @@
         <v>87.52340425531915</v>
       </c>
       <c r="L3" t="n">
-        <v>1.083174737435681</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P3" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R3" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U3" s="1" t="n">
+        <v>1.129760329363329</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V3" s="3" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -3490,16 +3552,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>21.75563463819692</v>
+        <v>22.9043860525527</v>
       </c>
       <c r="D4" t="n">
-        <v>30.29357719755566</v>
+        <v>25.2071166644031</v>
       </c>
       <c r="E4" t="n">
         <v>12.90931103415266</v>
       </c>
       <c r="F4" t="n">
-        <v>0.110367734282325</v>
+        <v>0.1034568888000799</v>
       </c>
       <c r="G4" t="n">
         <v>1752</v>
@@ -3517,108 +3579,108 @@
         <v>31.93243243243243</v>
       </c>
       <c r="L4" t="n">
-        <v>1.234901429018463</v>
-      </c>
-      <c r="M4" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P4" s="3" t="n">
+        <v>1.289464130119082</v>
+      </c>
+      <c r="M4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>0.75</v>
+      <c r="Q4" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>TCS</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Tata Consultancy Services Ltd</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>45.4199714271639</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>61.29852272007671</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="C5" s="5" t="n">
+        <v>50.94431367348518</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>60.2081007004365</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>19.13671215020777</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0.08912754322873048</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F5" s="5" t="n">
+        <v>0.0886406082507266</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>50429</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>7.871172131953608</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>10.4636148017166</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>8.618771612987096</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>87.09511568123393</v>
       </c>
-      <c r="L5" s="4" t="n">
-        <v>1.495078324768501</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V5" s="4" t="n">
+      <c r="L5" s="5" t="n">
+        <v>1.655940662120545</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V5" s="5" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3634,16 +3696,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>9.063752552370868</v>
+        <v>8.987963553189097</v>
       </c>
       <c r="D6" t="n">
-        <v>19.0758751448334</v>
+        <v>9.207012257755256</v>
       </c>
       <c r="E6" t="n">
         <v>4.60996999769213</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07694925508583529</v>
+        <v>0.09512917619708275</v>
       </c>
       <c r="G6" t="n">
         <v>5058</v>
@@ -3661,86 +3723,86 @@
         <v>13.85969387755102</v>
       </c>
       <c r="L6" t="n">
-        <v>1.214093912718612</v>
-      </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="n">
-        <v>0.5</v>
+        <v>1.205033720364319</v>
+      </c>
+      <c r="M6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V6" s="3" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>22.80943738656987</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>34.41057509442049</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>23.01393141233172</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>27.05313357020305</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>14.29312274253273</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>0.08912754322873048</v>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="F7" s="6" t="n">
+        <v>0.09486358890553362</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>15840</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>9.194090295112023</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="6" t="n">
         <v>12.71029997837341</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>9.407036350794119</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <v>46.46112115732369</v>
       </c>
-      <c r="L7" s="5" t="n">
-        <v>1.214093912718612</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr"/>
+      <c r="L7" s="6" t="n">
+        <v>1.205033720364319</v>
+      </c>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3756,137 +3818,137 @@
   <dimension ref="A1:V6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -3904,16 +3966,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10.08715713919508</v>
+        <v>10.73230601390972</v>
       </c>
       <c r="D2" t="n">
-        <v>609.8344810921832</v>
+        <v>645.952868852459</v>
       </c>
       <c r="E2" t="n">
         <v>1.551013972921306</v>
       </c>
       <c r="F2" t="n">
-        <v>0.06088182517303255</v>
+        <v>0.06477567162143734</v>
       </c>
       <c r="G2" t="n">
         <v>-2893</v>
@@ -3931,36 +3993,36 @@
         <v>192.2895238095238</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3013526154028893</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.3352704278677314</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="N2" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="T2" s="3" t="n">
         <v>0.6667</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="T2" s="2" t="n">
+      <c r="U2" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="U2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="V2" s="1" t="n">
+      <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -3976,16 +4038,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.352687057197166</v>
+        <v>7.732848705134029</v>
       </c>
       <c r="D3" t="n">
-        <v>796.04285467427</v>
+        <v>753.9778779188856</v>
       </c>
       <c r="E3" t="n">
         <v>0.942341125272681</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.1090413448432531</v>
       </c>
       <c r="G3" t="n">
         <v>105</v>
@@ -4003,105 +4065,109 @@
         <v>31.02154882154882</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2763050808045576</v>
+        <v>0.3020290902037117</v>
       </c>
       <c r="M3" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P3" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="N3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="3" t="n">
+      <c r="Q3" s="2" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T3" s="3" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="U3" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Life Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>49.44710986501021</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>39.05035832114759</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>4.836600998148862</v>
+      </c>
+      <c r="F4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="P3" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="inlineStr">
-        <is>
-          <t>Life Insurance Corporation of India</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="n">
-        <v>41.90624455892745</v>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>48.75521009350005</v>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>4.836600998148862</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>0.000102420189067669</v>
-      </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>853</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>73.17556747076097</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>8.15986061977938</v>
       </c>
-      <c r="J4" s="4" t="inlineStr"/>
-      <c r="K4" s="4" t="n">
+      <c r="J4" s="5" t="n">
+        <v/>
+      </c>
+      <c r="K4" s="5" t="n">
         <v>371.9375</v>
       </c>
-      <c r="L4" s="4" t="n">
-        <v>0.1479188847377071</v>
-      </c>
-      <c r="M4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="4" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="O4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="P4" s="4" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="Q4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="inlineStr"/>
-      <c r="U4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="V4" s="4" t="n">
-        <v>0</v>
+      <c r="L4" s="5" t="n">
+        <v>0.1591344094587576</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="O4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="5" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="T4" s="5" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="5" t="n">
+        <v>0.25</v>
       </c>
     </row>
     <row r="5">
@@ -4116,10 +4182,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>11.64893289870226</v>
+        <v>12.70458814059566</v>
       </c>
       <c r="D5" t="n">
-        <v>13.30340119318531</v>
+        <v>1.140327341024953</v>
       </c>
       <c r="E5" t="n">
         <v>1.434978937479165</v>
@@ -4143,86 +4209,86 @@
         <v>240.3333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2942895939103272</v>
+        <v>0.3313791900054984</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.25</v>
+      </c>
+      <c r="O5" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.5</v>
       </c>
       <c r="R5" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="S5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T5" s="1" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="S5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T5" s="2" t="n">
         <v>1</v>
       </c>
       <c r="U5" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
       <c r="V5" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr"/>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>10.86804501894867</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>329.2948455928416</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr"/>
+      <c r="C6" s="6" t="n">
+        <v>11.71844707725269</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>342.5016135868033</v>
+      </c>
+      <c r="E6" s="6" t="n">
         <v>1.492996455200235</v>
       </c>
-      <c r="F6" s="5" t="n">
-        <v>5.121009453383451e-05</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="F6" s="6" t="n">
+        <v>0.03238783581071867</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>-997</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>5.814576884099387</v>
       </c>
-      <c r="I6" s="5" t="n">
+      <c r="I6" s="6" t="n">
         <v>19.00683698090717</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>3.131030647754507</v>
       </c>
-      <c r="K6" s="5" t="n">
+      <c r="K6" s="6" t="n">
         <v>216.3114285714286</v>
       </c>
-      <c r="L6" s="5" t="n">
-        <v>0.2852973373574424</v>
-      </c>
-      <c r="M6" s="5" t="inlineStr"/>
-      <c r="N6" s="5" t="inlineStr"/>
-      <c r="O6" s="5" t="inlineStr"/>
-      <c r="P6" s="5" t="inlineStr"/>
-      <c r="Q6" s="5" t="inlineStr"/>
-      <c r="R6" s="5" t="inlineStr"/>
-      <c r="S6" s="5" t="inlineStr"/>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
-      <c r="V6" s="5" t="inlineStr"/>
+      <c r="L6" s="6" t="n">
+        <v>0.316704140104605</v>
+      </c>
+      <c r="M6" s="6" t="n"/>
+      <c r="N6" s="6" t="n"/>
+      <c r="O6" s="6" t="n"/>
+      <c r="P6" s="6" t="n"/>
+      <c r="Q6" s="6" t="n"/>
+      <c r="R6" s="6" t="n"/>
+      <c r="S6" s="6" t="n"/>
+      <c r="T6" s="6" t="n"/>
+      <c r="U6" s="6" t="n"/>
+      <c r="V6" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4238,137 +4304,137 @@
   <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -4386,16 +4452,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>34.83296156040878</v>
+        <v>35.51133734382231</v>
       </c>
       <c r="D2" t="n">
-        <v>34.64570403270877</v>
+        <v>28.64920066956402</v>
       </c>
       <c r="E2" t="n">
         <v>5.994201967046283</v>
       </c>
       <c r="F2" t="n">
-        <v>0.763604295274161</v>
+        <v>0.7218747934157467</v>
       </c>
       <c r="G2" t="n">
         <v>25415</v>
@@ -4413,36 +4479,36 @@
         <v>11.35550735116896</v>
       </c>
       <c r="L2" t="n">
-        <v>2.121343963337847</v>
-      </c>
-      <c r="M2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V2" s="1" t="n">
+        <v>2.213651947949293</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P2" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -4458,16 +4524,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.81615339641327</v>
+        <v>12.86154006000234</v>
       </c>
       <c r="D3" t="n">
-        <v>16.42095494049748</v>
+        <v>10.77223633731818</v>
       </c>
       <c r="E3" t="n">
         <v>7.433122166511544</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2342469185886957</v>
+        <v>0.2830499889606088</v>
       </c>
       <c r="G3" t="n">
         <v>4360</v>
@@ -4485,37 +4551,37 @@
         <v>23.62447844228095</v>
       </c>
       <c r="L3" t="n">
-        <v>1.032863267410399</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="2" t="n">
-        <v>0.5</v>
+        <v>1.068088347296268</v>
+      </c>
+      <c r="M3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q3" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="3" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -4526,21 +4592,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Indian Oil Corporation
-</t>
+          <t>Indian Oil Corporation</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23.79773496686259</v>
+        <v>23.53162465856491</v>
       </c>
       <c r="D4" t="n">
-        <v>23.50427970194363</v>
+        <v>18.91502792323878</v>
       </c>
       <c r="E4" t="n">
         <v>5.559462717942377</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9009461530827167</v>
+        <v>0.7230954600718581</v>
       </c>
       <c r="G4" t="n">
         <v>39635</v>
@@ -4558,37 +4623,37 @@
         <v>10.28232457809923</v>
       </c>
       <c r="L4" t="n">
-        <v>1.5213340910427</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O4" s="3" t="n">
+        <v>1.608409660170339</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O4" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S4" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V4" s="1" t="n">
-        <v>0.75</v>
+      <c r="Q4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="5">
@@ -4603,16 +4668,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.20916554065562</v>
+        <v>16.94039813688551</v>
       </c>
       <c r="D5" t="n">
-        <v>21.29909059979954</v>
+        <v>15.10899518817912</v>
       </c>
       <c r="E5" t="n">
         <v>9.655290194725701</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5435766274171389</v>
+        <v>0.4544486308481918</v>
       </c>
       <c r="G5" t="n">
         <v>42060</v>
@@ -4630,159 +4695,158 @@
         <v>11.361290955464</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7806033151446515</v>
-      </c>
-      <c r="M5" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q5" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V5" s="2" t="n">
-        <v>0.25</v>
+        <v>0.8332173339682772</v>
+      </c>
+      <c r="M5" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q5" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V5" s="3" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>RELIANCE</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Reliance Industries Ltd
-</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="n">
-        <v>9.64301796442261</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>15.18099743580594</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Reliance Industries Ltd</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.958650553699458</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.915648413697072</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>8.789365557299389</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>0.4362971396773213</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="F6" s="5" t="n">
+        <v>0.5784524141094746</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>45207</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>14.68063260349559</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>9.606097094616972</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="5" t="n">
         <v>11.95266483252204</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <v>7.728912535686478</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0.4953058277593309</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0</v>
+      <c r="L6" s="5" t="n">
+        <v>0.5122600635424216</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>16.20916554065562</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>21.29909059979954</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>16.94039813688551</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>15.10899518817912</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>7.433122166511544</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>0.5435766274171389</v>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="F7" s="6" t="n">
+        <v>0.5784524141094746</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>39635</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>14.68063260349559</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="6" t="n">
         <v>8.483226324685255</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>11.95266483252204</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <v>11.35550735116896</v>
       </c>
-      <c r="L7" s="5" t="n">
-        <v>1.032863267410399</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr"/>
+      <c r="L7" s="6" t="n">
+        <v>1.068088347296268</v>
+      </c>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4798,137 +4862,137 @@
   <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -4942,21 +5006,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cipla Ltd
-</t>
+          <t>Cipla Ltd</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>14.64584141310863</v>
+        <v>15.55455702838313</v>
       </c>
       <c r="D2" t="n">
-        <v>67.67624202053844</v>
+        <v>67.603154227031</v>
       </c>
       <c r="E2" t="n">
         <v>16.11701714906495</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01625356979162994</v>
+        <v>0.02093162585186849</v>
       </c>
       <c r="G2" t="n">
         <v>1152</v>
@@ -4974,36 +5037,36 @@
         <v>35.33876811594203</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7437310633386236</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P2" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V2" s="1" t="n">
+        <v>0.7922417237881536</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q2" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V2" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5019,16 +5082,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>11.66435809579354</v>
+        <v>11.78984599513669</v>
       </c>
       <c r="D3" t="n">
-        <v>18.54280510018215</v>
+        <v>13.49639015765434</v>
       </c>
       <c r="E3" t="n">
         <v>20.39515615041428</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000583217904789677</v>
+        <v>0.0002210596124088129</v>
       </c>
       <c r="G3" t="n">
         <v>992</v>
@@ -5046,37 +5109,37 @@
         <v>636.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5033363274733735</v>
-      </c>
-      <c r="M3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0</v>
+        <v>0.5074385510996119</v>
+      </c>
+      <c r="M3" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N3" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q3" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R3" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S3" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T3" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="4" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="4">
@@ -5091,16 +5154,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.14042733097011</v>
+        <v>19.74233736816026</v>
       </c>
       <c r="D4" t="n">
-        <v>24.83498581580204</v>
+        <v>21.36105235325225</v>
       </c>
       <c r="E4" t="n">
         <v>19.9136053693192</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1578587921558425</v>
+        <v>0.07085722375592836</v>
       </c>
       <c r="G4" t="n">
         <v>509</v>
@@ -5118,109 +5181,109 @@
         <v>51.70760233918129</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5994478685156651</v>
-      </c>
-      <c r="M4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7223053120165034</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P4" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q4" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>SUNPHARMA</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Sun Pharmaceuticals Industries Ltd</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>13.90436229472618</v>
-      </c>
-      <c r="D5" s="4" t="n">
-        <v>19.36613332961346</v>
-      </c>
-      <c r="E5" s="4" t="n">
+      <c r="C5" s="5" t="n">
+        <v>15.09416181067115</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>15.62719409629375</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>19.81565870053818</v>
       </c>
-      <c r="F5" s="4" t="n">
-        <v>0.03721334008536497</v>
-      </c>
-      <c r="G5" s="4" t="n">
+      <c r="F5" s="5" t="n">
+        <v>0.05142381453500244</v>
+      </c>
+      <c r="G5" s="5" t="n">
         <v>11372</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>24.53682964293125</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>10.78116321985565</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>29.45936165164078</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>58.33193277310924</v>
       </c>
-      <c r="L5" s="4" t="n">
-        <v>0.5503767760679105</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N5" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O5" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P5" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>0.25</v>
+      <c r="L5" s="5" t="n">
+        <v>0.5684929901064378</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O5" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V5" s="5" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -5235,16 +5298,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>22.0682302771855</v>
+        <v>24.15402567094516</v>
       </c>
       <c r="D6" t="n">
-        <v>33.05116629044394</v>
+        <v>23.53373781945211</v>
       </c>
       <c r="E6" t="n">
         <v>15.43624161073826</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4168443496801706</v>
+        <v>0.5866394399066511</v>
       </c>
       <c r="G6" t="n">
         <v>3106</v>
@@ -5262,86 +5325,86 @@
         <v>9.926553672316384</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7110286320254506</v>
-      </c>
-      <c r="M6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O6" s="3" t="n">
+        <v>0.7396070320579111</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="P6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1" t="n">
-        <v>0.75</v>
+      <c r="Q6" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>14.64584141310863</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>24.83498581580204</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>15.55455702838313</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>21.36105235325225</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>19.81565870053818</v>
       </c>
-      <c r="F7" s="5" t="n">
-        <v>0.03721334008536497</v>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="F7" s="6" t="n">
+        <v>0.05142381453500244</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>1152</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>23.39250464543747</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="6" t="n">
         <v>9.664930361854074</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>23.84240955838754</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <v>51.70760233918129</v>
       </c>
-      <c r="L7" s="5" t="n">
-        <v>0.5994478685156651</v>
-      </c>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr"/>
+      <c r="L7" s="6" t="n">
+        <v>0.7223053120165034</v>
+      </c>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5357,137 +5420,137 @@
   <dimension ref="A1:V9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -5505,56 +5568,64 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11.91376701966717</v>
+        <v>12.81269066503966</v>
       </c>
       <c r="D2" t="n">
-        <v>10.9991539112376</v>
+        <v>7.249772398650458</v>
       </c>
       <c r="E2" t="n">
         <v>13.66594360086768</v>
       </c>
       <c r="F2" t="n">
-        <v>6.375756429652042</v>
+        <v>6.595281675818589</v>
       </c>
       <c r="G2" t="n">
         <v>-13347</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v/>
+      </c>
       <c r="I2" t="n">
         <v>34.97617292638284</v>
       </c>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v/>
+      </c>
       <c r="K2" t="n">
         <v>1.713943268078306</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09383459870951984</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="P2" s="3" t="n">
+        <v>0.1046704357105556</v>
+      </c>
+      <c r="M2" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="N2" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="P2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" s="3" t="n">
-        <v>0</v>
+      <c r="Q2" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="R2" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="4" t="n">
+        <v>0.1429</v>
       </c>
       <c r="V2" s="3" t="n">
-        <v>0</v>
+        <v>0.2857</v>
       </c>
     </row>
     <row r="3">
@@ -5569,55 +5640,63 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>37.22522071701755</v>
+        <v>48.27674122146251</v>
       </c>
       <c r="D3" t="n">
-        <v>30.01420045057069</v>
+        <v>18.38582322758195</v>
       </c>
       <c r="E3" t="n">
         <v>41.36759945184802</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6738570969010258</v>
+        <v>0.8023177656738903</v>
       </c>
       <c r="G3" t="n">
         <v>17651</v>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="n">
+        <v/>
+      </c>
       <c r="I3" t="n">
         <v>16.08609641044097</v>
       </c>
-      <c r="J3" t="inlineStr"/>
+      <c r="J3" t="n">
+        <v/>
+      </c>
       <c r="K3" t="n">
         <v>8.297225501770956</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4544970392836511</v>
-      </c>
-      <c r="M3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O3" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="P3" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="V3" s="1" t="n">
+        <v>0.5472399439185297</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="R3" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="T3" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="V3" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -5633,16 +5712,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.167101640985306</v>
+        <v>8.280529953917052</v>
       </c>
       <c r="D4" t="n">
-        <v>9.951720386236911</v>
+        <v>7.15389752886175</v>
       </c>
       <c r="E4" t="n">
         <v>15.01828312728539</v>
       </c>
       <c r="F4" t="n">
-        <v>1.103035286546781</v>
+        <v>1.515600998463902</v>
       </c>
       <c r="G4" t="n">
         <v>-1963</v>
@@ -5660,37 +5739,37 @@
         <v>2.851436921578178</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1768927493377687</v>
-      </c>
-      <c r="M4" s="3" t="n">
-        <v>0</v>
+        <v>0.1988332438935725</v>
+      </c>
+      <c r="M4" s="4" t="n">
+        <v>0.1429</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P4" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.2857</v>
+      </c>
+      <c r="O4" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.2857</v>
       </c>
       <c r="Q4" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="R4" s="1" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="R4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="T4" s="1" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="T4" s="2" t="n">
         <v>1</v>
       </c>
       <c r="U4" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="V4" s="2" t="n">
-        <v>0.3333</v>
+        <v>0.2857</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>0.5714</v>
       </c>
     </row>
     <row r="5">
@@ -5701,21 +5780,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">NHPC Ltd
-</t>
+          <t>NHPC Ltd</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10.03262845899026</v>
+        <v>10.40773086662188</v>
       </c>
       <c r="D5" t="n">
-        <v>9.193238209228204</v>
+        <v>5.083984676480081</v>
       </c>
       <c r="E5" t="n">
         <v>41.81893687707641</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8520760168372812</v>
+        <v>0.8413260296625498</v>
       </c>
       <c r="G5" t="n">
         <v>970</v>
@@ -5733,109 +5811,109 @@
         <v>11.24342105263158</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09860668912070925</v>
+        <v>0.1032401899310803</v>
       </c>
       <c r="M5" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="N5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P5" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="Q5" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="R5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="3" t="n">
-        <v>0</v>
+        <v>0.2857</v>
+      </c>
+      <c r="N5" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="Q5" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>0.1429</v>
       </c>
       <c r="T5" s="3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="3" t="n">
-        <v>0.1667</v>
+        <v>0.3</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>0.1429</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>NTPC</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>NTPC Ltd</t>
         </is>
       </c>
-      <c r="C6" s="4" t="n">
-        <v>12.67709422839213</v>
-      </c>
-      <c r="D6" s="4" t="n">
-        <v>13.8066349648168</v>
-      </c>
-      <c r="E6" s="4" t="n">
+      <c r="C6" s="5" t="n">
+        <v>13.27359840706863</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8.860826310008269</v>
+      </c>
+      <c r="E6" s="5" t="n">
         <v>11.95063332978527</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>1.438201245602358</v>
-      </c>
-      <c r="G6" s="4" t="n">
+      <c r="F6" s="5" t="n">
+        <v>1.475521125007778</v>
+      </c>
+      <c r="G6" s="5" t="n">
         <v>8644</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>8.735165684951163</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>12.22230965433799</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="5" t="n">
         <v>8.447177119769854</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <v>4.604991464108609</v>
       </c>
-      <c r="L6" s="4" t="n">
-        <v>0.3626373849623143</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O6" s="4" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="P6" s="4" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="Q6" s="4" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="R6" s="4" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="V6" s="4" t="n">
-        <v>0.6667</v>
+      <c r="L6" s="5" t="n">
+        <v>0.3724372910920176</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="N6" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="O6" s="5" t="n">
+        <v>0.2857</v>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="Q6" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="R6" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S6" s="5" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="T6" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U6" s="5" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="V6" s="5" t="n">
+        <v>0.7143</v>
       </c>
     </row>
     <row r="7">
@@ -5850,16 +5928,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>16.91595789748102</v>
+        <v>17.87001124549607</v>
       </c>
       <c r="D7" t="n">
-        <v>18.81479203649087</v>
+        <v>12.68904690926698</v>
       </c>
       <c r="E7" t="n">
         <v>33.97028990249329</v>
       </c>
       <c r="F7" t="n">
-        <v>1.331378107993613</v>
+        <v>1.417345603929039</v>
       </c>
       <c r="G7" t="n">
         <v>24176</v>
@@ -5877,37 +5955,37 @@
         <v>4.60298643565485</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1795673274656577</v>
-      </c>
-      <c r="M7" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="N7" s="1" t="n">
-        <v>0.8333</v>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="P7" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S7" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="T7" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U7" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V7" s="2" t="n">
-        <v>0.5</v>
+        <v>0.1827659481160472</v>
+      </c>
+      <c r="M7" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>0.8571</v>
+      </c>
+      <c r="O7" s="3" t="n">
+        <v>0.7143</v>
+      </c>
+      <c r="P7" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="Q7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S7" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="T7" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U7" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="V7" s="3" t="n">
+        <v>0.4286</v>
       </c>
     </row>
     <row r="8">
@@ -5918,21 +5996,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tata Power Company Ltd
-</t>
+          <t>Tata Power Company Ltd</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>12.70783847980998</v>
+        <v>13.22784027691927</v>
       </c>
       <c r="D8" t="n">
-        <v>15.38252494727917</v>
+        <v>8.076006740658958</v>
       </c>
       <c r="E8" t="n">
         <v>6.965125551270159</v>
       </c>
       <c r="F8" t="n">
-        <v>1.731413301662708</v>
+        <v>1.659321300531586</v>
       </c>
       <c r="G8" t="n">
         <v>3569</v>
@@ -5950,86 +6027,86 @@
         <v>3.054392402331103</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4234066009784331</v>
-      </c>
-      <c r="M8" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="N8" s="2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="O8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="3" t="n">
-        <v>0.1667</v>
-      </c>
-      <c r="Q8" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R8" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S8" s="2" t="n">
-        <v>0.6667</v>
+        <v>0.4419074604110633</v>
+      </c>
+      <c r="M8" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="O8" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="P8" s="4" t="n">
+        <v>0.1429</v>
+      </c>
+      <c r="Q8" s="3" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="R8" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S8" s="3" t="n">
+        <v>0.7143</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="U8" s="2" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="V8" s="1" t="n">
-        <v>0.8333</v>
+        <v>0.3</v>
+      </c>
+      <c r="U8" s="3" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0.8571</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr"/>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>12.67709422839213</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>13.8066349648168</v>
-      </c>
-      <c r="E9" s="5" t="n">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>13.22784027691927</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>8.076006740658958</v>
+      </c>
+      <c r="E9" s="6" t="n">
         <v>15.01828312728539</v>
       </c>
-      <c r="F9" s="5" t="n">
-        <v>1.331378107993613</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="F9" s="6" t="n">
+        <v>1.475521125007778</v>
+      </c>
+      <c r="G9" s="6" t="n">
         <v>3569</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <v>9.189188268434778</v>
       </c>
-      <c r="I9" s="5" t="n">
+      <c r="I9" s="6" t="n">
         <v>12.22230965433799</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <v>8.447177119769854</v>
       </c>
-      <c r="K9" s="5" t="n">
+      <c r="K9" s="6" t="n">
         <v>4.60298643565485</v>
       </c>
-      <c r="L9" s="5" t="n">
-        <v>0.1795673274656577</v>
-      </c>
-      <c r="M9" s="5" t="inlineStr"/>
-      <c r="N9" s="5" t="inlineStr"/>
-      <c r="O9" s="5" t="inlineStr"/>
-      <c r="P9" s="5" t="inlineStr"/>
-      <c r="Q9" s="5" t="inlineStr"/>
-      <c r="R9" s="5" t="inlineStr"/>
-      <c r="S9" s="5" t="inlineStr"/>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
-      <c r="V9" s="5" t="inlineStr"/>
+      <c r="L9" s="6" t="n">
+        <v>0.1988332438935725</v>
+      </c>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="6" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n"/>
+      <c r="R9" s="6" t="n"/>
+      <c r="S9" s="6" t="n"/>
+      <c r="T9" s="6" t="n"/>
+      <c r="U9" s="6" t="n"/>
+      <c r="V9" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6045,137 +6122,137 @@
   <dimension ref="A1:V7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="32" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="29" customWidth="1" min="13" max="13"/>
-    <col width="39" customWidth="1" min="14" max="14"/>
-    <col width="30" customWidth="1" min="15" max="15"/>
-    <col width="23" customWidth="1" min="16" max="16"/>
-    <col width="26" customWidth="1" min="17" max="17"/>
-    <col width="21" customWidth="1" min="18" max="18"/>
-    <col width="25" customWidth="1" min="19" max="19"/>
-    <col width="21" customWidth="1" min="20" max="20"/>
-    <col width="26" customWidth="1" min="21" max="21"/>
-    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="14" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="14" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>company_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>company_name</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>return_on_equity_pct_pctile</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>return_on_capital_employed_pct_pctile</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>net_profit_margin_pct_pctile</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>debt_to_equity_pctile</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>free_cash_flow_cr_pctile</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>pat_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>revenue_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>eps_cagr_5yr_pctile</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>interest_coverage_pctile</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>asset_turnover_pctile</t>
         </is>
@@ -6196,7 +6273,7 @@
         <v>15.83271240518905</v>
       </c>
       <c r="D2" t="n">
-        <v>2.613326906856248</v>
+        <v>2.520716781712082</v>
       </c>
       <c r="E2" t="n">
         <v>22.73130411725443</v>
@@ -6222,107 +6299,107 @@
       <c r="L2" t="n">
         <v>0.0720367478374617</v>
       </c>
-      <c r="M2" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="N2" s="3" t="n">
+      <c r="M2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N2" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P2" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="P2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="R2" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="S2" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="T2" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U2" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="V2" s="2" t="n">
-        <v>0.5</v>
+      <c r="Q2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S2" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="V2" s="3" t="n">
+        <v>0.6</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>HDFCBANK</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>HDFC Bank Ltd</t>
         </is>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>14.33974005030719</v>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>4.887343889375092</v>
-      </c>
-      <c r="E3" s="4" t="n">
+      <c r="D3" s="5" t="n">
+        <v>4.801033923800871</v>
+      </c>
+      <c r="E3" s="5" t="n">
         <v>23.07288232992184</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>6.808786667718385</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>35669</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>23.86506357287907</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>21.95098428169122</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="5" t="n">
         <v>15.42478808253083</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="5" t="n">
         <v>1.400768822479211</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="5" t="n">
         <v>0.07038097917866981</v>
       </c>
-      <c r="M3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="P3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Q3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="S3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" s="4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="V3" s="4" t="n">
-        <v>0.25</v>
+      <c r="M3" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="N3" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O3" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Q3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="R3" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="5" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U3" s="5" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="V3" s="5" t="n">
+        <v>0.4</v>
       </c>
     </row>
     <row r="4">
@@ -6340,7 +6417,7 @@
         <v>17.99027109750765</v>
       </c>
       <c r="D4" t="n">
-        <v>5.219877597590544</v>
+        <v>5.11888931768417</v>
       </c>
       <c r="E4" t="n">
         <v>28.8880112339828</v>
@@ -6366,35 +6443,35 @@
       <c r="L4" t="n">
         <v>0.06747535915921023</v>
       </c>
-      <c r="M4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="N4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="O4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="P4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="Q4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="R4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="S4" s="1" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="T4" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="U4" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>0</v>
+      <c r="M4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P4" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="S4" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -6412,7 +6489,7 @@
         <v>14.25227319776422</v>
       </c>
       <c r="D5" t="n">
-        <v>3.563199589661572</v>
+        <v>3.475962286021232</v>
       </c>
       <c r="E5" t="n">
         <v>19.56369677362945</v>
@@ -6438,34 +6515,34 @@
       <c r="L5" t="n">
         <v>0.08884228106460039</v>
       </c>
-      <c r="M5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="N5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Q5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="R5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="S5" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T5" s="2" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="U5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="V5" s="1" t="n">
+      <c r="M5" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="O5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Q5" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S5" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T5" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V5" s="2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -6477,15 +6554,14 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kotak Mahindra Bank Ltd
-</t>
+          <t>Kotak Mahindra Bank Ltd</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>14.01301818853291</v>
       </c>
       <c r="D6" t="n">
-        <v>7.231227684955393</v>
+        <v>7.113136699541475</v>
       </c>
       <c r="E6" t="n">
         <v>32.38615146611662</v>
@@ -6511,84 +6587,84 @@
       <c r="L6" t="n">
         <v>0.07325702420450533</v>
       </c>
-      <c r="M6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="P6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="R6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1" t="n">
-        <v>0.75</v>
+      <c r="M6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="P6" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q6" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T6" s="3" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="U6" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.8</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr"/>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>PEER GROUP MEDIAN</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="n">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>MEDIAN</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
         <v>14.33974005030719</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>4.887343889375092</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="D7" s="6" t="n">
+        <v>4.801033923800871</v>
+      </c>
+      <c r="E7" s="6" t="n">
         <v>23.07288232992184</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>6.808786667718385</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>6766</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>23.86506357287907</v>
       </c>
-      <c r="I7" s="5" t="n">
+      <c r="I7" s="6" t="n">
         <v>15.49561308335803</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>19.34407044160125</v>
       </c>
-      <c r="K7" s="5" t="n">
+      <c r="K7" s="6" t="n">
         <v>1.400768822479211</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L7" s="6" t="n">
         <v>0.0720367478374617</v>
       </c>
-      <c r="M7" s="5" t="inlineStr"/>
-      <c r="N7" s="5" t="inlineStr"/>
-      <c r="O7" s="5" t="inlineStr"/>
-      <c r="P7" s="5" t="inlineStr"/>
-      <c r="Q7" s="5" t="inlineStr"/>
-      <c r="R7" s="5" t="inlineStr"/>
-      <c r="S7" s="5" t="inlineStr"/>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
-      <c r="V7" s="5" t="inlineStr"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="6" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="6" t="n"/>
+      <c r="R7" s="6" t="n"/>
+      <c r="S7" s="6" t="n"/>
+      <c r="T7" s="6" t="n"/>
+      <c r="U7" s="6" t="n"/>
+      <c r="V7" s="6" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
